--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/feb-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/feb-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>52090584</v>
+        <v>60428.51</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>47691000.49</v>
+        <v>55324.7</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>47691000.49</v>
+        <v>55324.7</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>39951000.11</v>
+        <v>46345.79</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>24560900.28</v>
+        <v>28492.26</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>32387040</v>
+        <v>37571.1</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>44970100</v>
+        <v>52168.28</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>51170000</v>
+        <v>59360.57</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>40470800.44</v>
+        <v>46948.8</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>32951100</v>
+        <v>38225.45</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>23527252</v>
+        <v>27293.16</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>29110899.79</v>
+        <v>33770.56</v>
       </c>
     </row>
     <row r="14">
@@ -1301,11 +1301,11 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>54385380</v>
+        <v>63090.62</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>13196698.97</v>
+        <v>15309.04</v>
       </c>
     </row>
     <row r="16">
@@ -1423,11 +1423,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>58797900</v>
+        <v>68209.44</v>
       </c>
     </row>
     <row r="17">
@@ -1484,11 +1484,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>9891000.35</v>
+        <v>11474.21</v>
       </c>
     </row>
     <row r="18">
@@ -1545,11 +1545,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>35042798.7</v>
+        <v>40651.96</v>
       </c>
     </row>
     <row r="19">
@@ -1606,11 +1606,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>34666277.94</v>
+        <v>40215.17</v>
       </c>
     </row>
     <row r="20">
@@ -1667,11 +1667,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>22485050</v>
+        <v>26084.14</v>
       </c>
     </row>
     <row r="21">
@@ -1728,11 +1728,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>27170999.87</v>
+        <v>31520.15</v>
       </c>
     </row>
     <row r="22">
@@ -1789,11 +1789,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>69332555.88</v>
+        <v>80430.33</v>
       </c>
     </row>
     <row r="23">
@@ -1850,11 +1850,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>25470899.23</v>
+        <v>29547.92</v>
       </c>
     </row>
     <row r="24">
@@ -1911,11 +1911,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>32387040</v>
+        <v>37571.1</v>
       </c>
     </row>
     <row r="25">
@@ -1976,11 +1976,11 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>189696199.49</v>
+        <v>220060.09</v>
       </c>
     </row>
     <row r="26">
@@ -2041,11 +2041,11 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>107174613</v>
+        <v>124329.61</v>
       </c>
     </row>
     <row r="27">
@@ -2106,11 +2106,11 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>134196300</v>
+        <v>155676.55</v>
       </c>
     </row>
     <row r="28">
@@ -2167,11 +2167,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>22676283</v>
+        <v>26305.98</v>
       </c>
     </row>
     <row r="29">
@@ -2228,11 +2228,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>19782000.7</v>
+        <v>22948.42</v>
       </c>
     </row>
     <row r="30">
@@ -2289,17 +2289,17 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>44425075.24</v>
+        <v>51536.01</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1079650-7-CM26</t>
+          <t>29-1421-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2319,103 +2319,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>32387040</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>29-1421-CM26</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2239-8-LR23</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>feb-2026</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>61.103.035-5</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>76.296.863-0</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="n">
-        <v>43542000</v>
+        <v>50511.59</v>
       </c>
     </row>
   </sheetData>
